--- a/app/public/freelancer-form-individual.xlsx
+++ b/app/public/freelancer-form-individual.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10927"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/juliekim/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D304B24C-3E7A-3F4E-9A99-812ECABEA113}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8C4C0BA-4EBF-6446-B418-C2184089D8CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="15540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -81,9 +81,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>이름</t>
-  </si>
-  <si>
     <t>성 명</t>
   </si>
   <si>
@@ -146,6 +143,10 @@
       </rPr>
       <t>서</t>
     </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>내역</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -268,7 +269,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="22">
+  <borders count="23">
     <border>
       <left/>
       <right/>
@@ -286,30 +287,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top style="double">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="double">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="double">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF000000"/>
       </left>
@@ -344,30 +321,6 @@
         <color rgb="FF000000"/>
       </top>
       <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="double">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="double">
         <color rgb="FF000000"/>
       </bottom>
       <diagonal/>
@@ -516,6 +469,69 @@
       </top>
       <bottom style="thin">
         <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -524,21 +540,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="4" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -556,7 +569,7 @@
     <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -565,131 +578,140 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="58" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="58" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -910,148 +932,148 @@
   <dimension ref="A2:G24"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="10.83203125" style="7"/>
-    <col min="2" max="2" width="17.5" style="6" customWidth="1"/>
-    <col min="3" max="3" width="6.33203125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" style="6"/>
-    <col min="5" max="5" width="14.83203125" style="6" customWidth="1"/>
-    <col min="6" max="6" width="10.83203125" style="7"/>
-    <col min="7" max="7" width="18.5" style="7" customWidth="1"/>
-    <col min="8" max="16384" width="10.83203125" style="7"/>
+    <col min="1" max="1" width="10.83203125" style="6"/>
+    <col min="2" max="2" width="17.5" style="5" customWidth="1"/>
+    <col min="3" max="3" width="6.33203125" style="5" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" style="5"/>
+    <col min="5" max="5" width="14.83203125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" style="6"/>
+    <col min="7" max="7" width="18.5" style="6" customWidth="1"/>
+    <col min="8" max="16384" width="10.83203125" style="6"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" ht="24" customHeight="1">
-      <c r="A2" s="54" t="s">
+      <c r="A2" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="42"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
+      <c r="F2" s="42"/>
+      <c r="G2" s="42"/>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="7"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4" s="7"/>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8"/>
+      <c r="D4" s="8"/>
+      <c r="E4" s="8"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="9"/>
+      <c r="C5" s="10"/>
+      <c r="D5" s="32" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="34"/>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="20" t="s">
+        <v>15</v>
+      </c>
+      <c r="E6" s="13"/>
+      <c r="F6" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="G6" s="14"/>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="11"/>
+      <c r="B7" s="15"/>
+      <c r="C7" s="10"/>
+      <c r="D7" s="21" t="s">
+        <v>3</v>
+      </c>
+      <c r="E7" s="35"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="37"/>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="C8" s="10"/>
+      <c r="D8" s="22" t="s">
+        <v>5</v>
+      </c>
+      <c r="E8" s="38"/>
+      <c r="F8" s="39"/>
+      <c r="G8" s="40"/>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="31"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="23" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="16"/>
+      <c r="F9" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="16"/>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="15"/>
+      <c r="B10" s="15"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="17"/>
+      <c r="B11" s="18"/>
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
-      <c r="D2" s="55"/>
-      <c r="E2" s="55"/>
-      <c r="F2" s="55"/>
-      <c r="G2" s="55"/>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="8"/>
-      <c r="B3" s="9"/>
-      <c r="C3" s="9"/>
-      <c r="D3" s="9"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="8"/>
-      <c r="B4" s="9"/>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="29" t="s">
-        <v>14</v>
-      </c>
-      <c r="B5" s="10"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="E5" s="46"/>
-      <c r="F5" s="46"/>
-      <c r="G5" s="47"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="30" t="s">
-        <v>1</v>
-      </c>
-      <c r="B6" s="13" t="s">
-        <v>2</v>
-      </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="23" t="s">
-        <v>16</v>
-      </c>
-      <c r="E6" s="14"/>
-      <c r="F6" s="27" t="s">
-        <v>11</v>
-      </c>
-      <c r="G6" s="15"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="12"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="E7" s="48"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="50"/>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="C8" s="11"/>
-      <c r="D8" s="25" t="s">
-        <v>5</v>
-      </c>
-      <c r="E8" s="51"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="53"/>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="43" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="44"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="17"/>
-      <c r="F9" s="28" t="s">
-        <v>13</v>
-      </c>
-      <c r="G9" s="17"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="16"/>
-      <c r="B10" s="16"/>
-      <c r="C10" s="9"/>
-      <c r="D10" s="9"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-    </row>
-    <row r="11" spans="1:7" ht="14" thickBot="1">
-      <c r="A11" s="18"/>
-      <c r="B11" s="19"/>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="8"/>
-      <c r="G11" s="8"/>
-    </row>
-    <row r="12" spans="1:7" ht="14" thickTop="1">
-      <c r="A12" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="B12" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="C12" s="33" t="s">
+      <c r="C12" s="29" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="33" t="s">
+      <c r="D12" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="33" t="s">
+      <c r="E12" s="46" t="s">
         <v>9</v>
       </c>
-      <c r="F12" s="41" t="s">
+      <c r="F12" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="G12" s="42"/>
+      <c r="G12" s="52"/>
     </row>
     <row r="13" spans="1:7">
       <c r="A13" s="1">
@@ -1059,10 +1081,10 @@
       </c>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="35"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="47"/>
+      <c r="F13" s="53"/>
+      <c r="G13" s="54"/>
     </row>
     <row r="14" spans="1:7">
       <c r="A14" s="1">
@@ -1070,10 +1092,10 @@
       </c>
       <c r="B14" s="2"/>
       <c r="C14" s="2"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="35"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="47"/>
+      <c r="F14" s="53"/>
+      <c r="G14" s="54"/>
     </row>
     <row r="15" spans="1:7">
       <c r="A15" s="1">
@@ -1081,10 +1103,10 @@
       </c>
       <c r="B15" s="2"/>
       <c r="C15" s="2"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="20"/>
-      <c r="F15" s="34"/>
-      <c r="G15" s="35"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="47"/>
+      <c r="F15" s="53"/>
+      <c r="G15" s="54"/>
     </row>
     <row r="16" spans="1:7">
       <c r="A16" s="1">
@@ -1092,10 +1114,10 @@
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="2"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="20"/>
-      <c r="F16" s="34"/>
-      <c r="G16" s="35"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="47"/>
+      <c r="F16" s="53"/>
+      <c r="G16" s="54"/>
     </row>
     <row r="17" spans="1:7">
       <c r="A17" s="1">
@@ -1103,10 +1125,10 @@
       </c>
       <c r="B17" s="2"/>
       <c r="C17" s="2"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="35"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="47"/>
+      <c r="F17" s="53"/>
+      <c r="G17" s="54"/>
     </row>
     <row r="18" spans="1:7">
       <c r="A18" s="1">
@@ -1114,10 +1136,10 @@
       </c>
       <c r="B18" s="2"/>
       <c r="C18" s="2"/>
-      <c r="D18" s="20"/>
-      <c r="E18" s="20"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="35"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="53"/>
+      <c r="G18" s="54"/>
     </row>
     <row r="19" spans="1:7">
       <c r="A19" s="1">
@@ -1125,10 +1147,10 @@
       </c>
       <c r="B19" s="2"/>
       <c r="C19" s="2"/>
-      <c r="D19" s="20"/>
-      <c r="E19" s="20"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="22"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="53"/>
+      <c r="G19" s="57"/>
     </row>
     <row r="20" spans="1:7">
       <c r="A20" s="1">
@@ -1137,9 +1159,9 @@
       <c r="B20" s="2"/>
       <c r="C20" s="3"/>
       <c r="D20" s="4"/>
-      <c r="E20" s="4"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="35"/>
+      <c r="E20" s="48"/>
+      <c r="F20" s="53"/>
+      <c r="G20" s="54"/>
     </row>
     <row r="21" spans="1:7">
       <c r="A21" s="1">
@@ -1148,9 +1170,9 @@
       <c r="B21" s="2"/>
       <c r="C21" s="3"/>
       <c r="D21" s="4"/>
-      <c r="E21" s="4"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="22"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="53"/>
+      <c r="G21" s="57"/>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" s="1">
@@ -1159,51 +1181,53 @@
       <c r="B22" s="2"/>
       <c r="C22" s="3"/>
       <c r="D22" s="4"/>
-      <c r="E22" s="5"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="35"/>
-    </row>
-    <row r="23" spans="1:7" ht="14" thickBot="1">
-      <c r="A23" s="36" t="s">
+      <c r="E22" s="49"/>
+      <c r="F22" s="53"/>
+      <c r="G22" s="54"/>
+    </row>
+    <row r="23" spans="1:7">
+      <c r="A23" s="43" t="s">
         <v>6</v>
       </c>
-      <c r="B23" s="37"/>
-      <c r="C23" s="37"/>
-      <c r="D23" s="38"/>
-      <c r="E23" s="31">
+      <c r="B23" s="44"/>
+      <c r="C23" s="44"/>
+      <c r="D23" s="45"/>
+      <c r="E23" s="50">
         <f>SUM(E13:E22)</f>
         <v>0</v>
       </c>
-      <c r="F23" s="39"/>
-      <c r="G23" s="40"/>
-    </row>
-    <row r="24" spans="1:7" ht="14" thickTop="1">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="9"/>
-      <c r="E24" s="9"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="8"/>
+      <c r="F23" s="55"/>
+      <c r="G23" s="56"/>
+    </row>
+    <row r="24" spans="1:7">
+      <c r="A24" s="7"/>
+      <c r="B24" s="8"/>
+      <c r="C24" s="8"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="8"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="7"/>
     </row>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="18">
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="F20:G20"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="F23:G23"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="F21:G21"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="F12:G12"/>
+    <mergeCell ref="F13:G13"/>
+    <mergeCell ref="F14:G14"/>
+    <mergeCell ref="F15:G15"/>
     <mergeCell ref="F16:G16"/>
     <mergeCell ref="F17:G17"/>
     <mergeCell ref="A9:B9"/>
     <mergeCell ref="D5:G5"/>
     <mergeCell ref="E7:G7"/>
     <mergeCell ref="E8:G8"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="F12:G12"/>
-    <mergeCell ref="F13:G13"/>
-    <mergeCell ref="F14:G14"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="F20:G20"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="F23:G23"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
